--- a/Exam/gymtrackerpro/app/admin/exercises/new/_components/__tests__/ft/create-exercise-form/create-exercise-form-ft-form.xlsx
+++ b/Exam/gymtrackerpro/app/admin/exercises/new/_components/__tests__/ft/create-exercise-form/create-exercise-form-ft-form.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="100">
   <si>
     <t>Component: CreateExerciseForm — CreateExerciseForm - validates new exercise input, calls createExercise, and redirects to the exercises list on success.</t>
   </si>
@@ -61,24 +61,6 @@
   </si>
   <si>
     <t>createExercise(valid payload) is called once on valid submit; router.push("/admin/exercises") is called only on success.</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Run: npx jest create-exercise-form.test.tsx --selectProjects jsdom</t>
-  </si>
-  <si>
-    <t>The test file intentionally has only the main describe("CreateExerciseForm") block.</t>
-  </si>
-  <si>
-    <t>Predicate coverage includes each createExerciseSchema field independently: name, description, muscleGroup, and equipmentNeeded.</t>
-  </si>
-  <si>
-    <t>The form uses noValidate so native browser required validation does not bypass the Zod validation branch and inline field-error UI.</t>
-  </si>
-  <si>
-    <t>Branch coverage includes validation failure, create success, create failure, server field errors, pending UI, and recovery after server error.</t>
   </si>
   <si>
     <t>No TC</t>
@@ -771,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -860,66 +842,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" ht="35" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -943,22 +870,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -966,22 +893,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -989,22 +916,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1012,22 +939,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1035,22 +962,22 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1058,22 +985,22 @@
         <v>1</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1081,22 +1008,22 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1104,22 +1031,22 @@
         <v>1</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1127,22 +1054,22 @@
         <v>1</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1150,22 +1077,22 @@
         <v>1</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1173,22 +1100,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1196,22 +1123,22 @@
         <v>1</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1219,22 +1146,22 @@
         <v>1</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1242,22 +1169,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1265,22 +1192,22 @@
         <v>1</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1310,17 +1237,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1332,40 +1259,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="J5" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1373,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4">
         <v>14</v>
@@ -1385,28 +1312,28 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25"/>
@@ -1415,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>4</v>
